--- a/data/trans_camb/P1002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,77</t>
+          <t>0,02; 5,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,91</t>
+          <t>-3,48; 2,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,39</t>
+          <t>-1,66; 4,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,05</t>
+          <t>7,01; 12,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,08</t>
+          <t>4,37; 10,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,53</t>
+          <t>6,45; 12,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,32</t>
+          <t>5,14; 9,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,29</t>
+          <t>1,96; 6,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,74</t>
+          <t>3,85; 8,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 68,84</t>
+          <t>0,32; 65,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 20,88</t>
+          <t>-32,28; 25,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 50,08</t>
+          <t>-15,29; 51,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,51; 112,65</t>
+          <t>49,16; 111,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 94,74</t>
+          <t>31,18; 94,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,64; 107,59</t>
+          <t>44,77; 103,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,04; 87,16</t>
+          <t>41,4; 88,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,95; 60,26</t>
+          <t>14,9; 57,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,95; 82,34</t>
+          <t>32,22; 80,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,07</t>
+          <t>0,59; 3,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,2</t>
+          <t>0,61; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,08</t>
+          <t>0,14; 3,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,39</t>
+          <t>1,57; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,24</t>
+          <t>-0,17; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,38</t>
+          <t>-1,35; 2,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,75</t>
+          <t>1,35; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,71</t>
+          <t>0,57; 2,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,41</t>
+          <t>-0,19; 2,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 146,16</t>
+          <t>16,45; 132,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 139,71</t>
+          <t>16,62; 135,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 140,0</t>
+          <t>5,83; 141,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,02; 100,22</t>
+          <t>22,93; 105,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 63,32</t>
+          <t>-2,75; 63,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 43,57</t>
+          <t>-19,66; 45,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,29; 95,86</t>
+          <t>27,54; 92,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 70,07</t>
+          <t>11,19; 66,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 61,28</t>
+          <t>-3,28; 59,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,24</t>
+          <t>-2,94; 1,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,6</t>
+          <t>-2,87; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,42</t>
+          <t>-2,0; 2,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,8</t>
+          <t>-2,56; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,36</t>
+          <t>-2,6; 2,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,05</t>
+          <t>-0,58; 4,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,64</t>
+          <t>-2,06; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,35</t>
+          <t>-2,11; 1,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,13</t>
+          <t>-0,42; 3,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 97,53</t>
+          <t>-64,23; 83,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 72,1</t>
+          <t>-63,12; 76,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 94,75</t>
+          <t>-44,1; 97,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 86,61</t>
+          <t>-41,99; 97,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 72,82</t>
+          <t>-42,98; 83,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 159,23</t>
+          <t>-11,34; 142,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 54,44</t>
+          <t>-41,08; 51,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 43,39</t>
+          <t>-41,49; 37,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 95,11</t>
+          <t>-7,95; 96,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,74</t>
+          <t>0,45; 2,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,3</t>
+          <t>-0,82; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,52</t>
+          <t>-1,21; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,93</t>
+          <t>3,98; 7,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,59</t>
+          <t>0,82; 3,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,08</t>
+          <t>-0,62; 2,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,45</t>
+          <t>2,49; 4,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,25; 2,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,87</t>
+          <t>-0,39; 1,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 57,89</t>
+          <t>8,1; 59,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 27,63</t>
+          <t>-14,72; 28,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 32,18</t>
+          <t>-21,2; 29,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,73; 89,29</t>
+          <t>43,13; 90,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 47,08</t>
+          <t>9,36; 47,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 38,34</t>
+          <t>-6,11; 37,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,33; 69,2</t>
+          <t>33,58; 70,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 33,22</t>
+          <t>3,42; 34,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 28,84</t>
+          <t>-5,42; 28,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>5,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,81</t>
+          <t>0,17; 6,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,16</t>
+          <t>-3,46; 2,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,5</t>
+          <t>-1,84; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,96</t>
+          <t>7,11; 13,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,9</t>
+          <t>4,51; 10,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,17</t>
+          <t>6,19; 11,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,32</t>
+          <t>4,96; 9,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,19</t>
+          <t>1,93; 6,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,66</t>
+          <t>3,66; 7,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 65,28</t>
+          <t>1,63; 72,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 25,5</t>
+          <t>-31,28; 25,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 51,41</t>
+          <t>-16,79; 45,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,16; 111,65</t>
+          <t>48,4; 113,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 94,14</t>
+          <t>32,07; 93,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,77; 103,91</t>
+          <t>42,09; 103,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,4; 88,29</t>
+          <t>39,08; 84,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 57,69</t>
+          <t>15,63; 59,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,22; 80,63</t>
+          <t>29,61; 72,56</t>
         </is>
       </c>
     </row>
@@ -850,24 +850,24 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>2,26</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,48</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1,76</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,53</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,04</t>
+          <t>0,37; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,09</t>
+          <t>0,58; 3,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,22</t>
+          <t>1,03; 3,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,4</t>
+          <t>1,57; 5,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,18</t>
+          <t>-0,26; 3,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,34</t>
+          <t>0,11; 3,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,6</t>
+          <t>1,39; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,63</t>
+          <t>0,58; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,33</t>
+          <t>1,03; 3,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,45; 132,96</t>
+          <t>8,27; 129,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 135,27</t>
+          <t>17,53; 129,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 141,05</t>
+          <t>25,17; 157,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,93; 105,76</t>
+          <t>24,47; 107,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 63,58</t>
+          <t>-4,15; 63,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 45,55</t>
+          <t>1,47; 63,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 92,11</t>
+          <t>26,78; 92,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 66,42</t>
+          <t>12,46; 71,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 59,14</t>
+          <t>19,66; 78,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,98</t>
+          <t>-2,88; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,78</t>
+          <t>-3,09; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,47</t>
+          <t>-2,26; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,21</t>
+          <t>-2,72; 3,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,42</t>
+          <t>-2,97; 2,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,88</t>
+          <t>0,19; 5,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,74</t>
+          <t>-2,05; 1,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,24</t>
+          <t>-2,38; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,08</t>
+          <t>-0,5; 3,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 83,7</t>
+          <t>-61,55; 83,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 76,06</t>
+          <t>-64,37; 61,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,1; 97,44</t>
+          <t>-43,79; 93,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 97,33</t>
+          <t>-44,98; 92,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 83,66</t>
+          <t>-49,28; 66,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 142,68</t>
+          <t>0,04; 163,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 51,21</t>
+          <t>-42,23; 60,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 37,64</t>
+          <t>-44,71; 35,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 96,8</t>
+          <t>-10,74; 97,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,73</t>
+          <t>0,36; 2,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,36</t>
+          <t>-0,96; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,38</t>
+          <t>-0,56; 1,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,06</t>
+          <t>3,83; 6,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,7</t>
+          <t>0,84; 3,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,9</t>
+          <t>0,91; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,53</t>
+          <t>2,5; 4,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,21</t>
+          <t>0,35; 2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,85</t>
+          <t>0,68; 2,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,1; 59,94</t>
+          <t>6,83; 59,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 28,67</t>
+          <t>-16,35; 26,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 29,02</t>
+          <t>-9,8; 34,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,13; 90,05</t>
+          <t>40,94; 87,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 47,65</t>
+          <t>8,87; 46,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 37,42</t>
+          <t>9,63; 44,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,58; 70,28</t>
+          <t>34,75; 71,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 34,15</t>
+          <t>4,65; 33,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 28,78</t>
+          <t>9,06; 36,58</t>
         </is>
       </c>
     </row>
